--- a/public/sample/enquiries_passout_sample_record_file.xlsx
+++ b/public/sample/enquiries_passout_sample_record_file.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="39">
   <si>
     <t>Name</t>
   </si>
@@ -53,27 +53,12 @@
     <t>Mobile</t>
   </si>
   <si>
-    <t>VIKAS MEHRA</t>
-  </si>
-  <si>
-    <t>vikas1.mehra@yopmail.com</t>
-  </si>
-  <si>
     <t>B.Tech</t>
   </si>
   <si>
-    <t>VIKASH SINGH</t>
-  </si>
-  <si>
     <t>vikas.singh@yopmail.com</t>
   </si>
   <si>
-    <t>ROHAN VERMA</t>
-  </si>
-  <si>
-    <t>rohan1.verma@yopmail.com</t>
-  </si>
-  <si>
     <t>BBA</t>
   </si>
   <si>
@@ -135,6 +120,36 @@
   </si>
   <si>
     <t>GURPREET KAU2R</t>
+  </si>
+  <si>
+    <t>["MBA","Civil","EC","Mechanical"]</t>
+  </si>
+  <si>
+    <t>abc</t>
+  </si>
+  <si>
+    <t>xyz,123</t>
+  </si>
+  <si>
+    <t>vik.mehra@yopmail.com</t>
+  </si>
+  <si>
+    <t>Vipin</t>
+  </si>
+  <si>
+    <t>virender SINGH</t>
+  </si>
+  <si>
+    <t>hemant VERMA</t>
+  </si>
+  <si>
+    <t>hemant.verma@yopmail.com</t>
+  </si>
+  <si>
+    <t>virs.singh@yopmail.com</t>
+  </si>
+  <si>
+    <t>Departments</t>
   </si>
 </sst>
 </file>
@@ -277,7 +292,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -311,6 +326,7 @@
     <xf numFmtId="3" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -614,7 +630,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F74"/>
+  <dimension ref="A1:G74"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="20.44140625" customWidth="1"/>
@@ -624,7 +640,7 @@
     <col min="6" max="6" width="41.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -643,205 +659,217 @@
       <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" ht="15.6">
-      <c r="A2" s="6" t="s">
+      <c r="G1" s="13" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="15.6">
+      <c r="A2" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D2" t="s">
         <v>6</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" t="s">
-        <v>31</v>
-      </c>
-      <c r="D2" t="s">
-        <v>8</v>
       </c>
       <c r="E2">
         <v>7</v>
       </c>
       <c r="F2" s="12">
-        <v>9876545678</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" t="s">
-        <v>10</v>
+        <v>1594959489</v>
+      </c>
+      <c r="G2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="C3" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E3">
         <v>8</v>
       </c>
       <c r="F3" s="5">
-        <v>8765678765</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="7" t="s">
-        <v>11</v>
+        <v>9898989911</v>
+      </c>
+      <c r="G3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="5" t="s">
+        <v>35</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="C4" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D4" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E4">
         <v>5</v>
       </c>
       <c r="F4" s="5">
-        <v>1111111111</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
+        <v>5555555551</v>
+      </c>
+      <c r="G4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
       <c r="A5" s="7" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C5" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D5" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E5">
         <v>5</v>
       </c>
       <c r="F5" s="5"/>
     </row>
-    <row r="6" spans="1:6" ht="15.6">
+    <row r="6" spans="1:7" ht="15.6">
       <c r="A6" s="7" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C6" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D6" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E6">
         <v>4</v>
       </c>
       <c r="F6" s="4"/>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:7">
       <c r="A7" s="7" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E7">
         <v>2</v>
       </c>
       <c r="F7" s="5"/>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:7">
       <c r="A8" s="7" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="B8" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C8" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D8" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E8">
         <v>7</v>
       </c>
       <c r="F8" s="5"/>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:7">
       <c r="A9" s="5" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="B9" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="C9" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D9" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="E9">
         <v>6</v>
       </c>
       <c r="F9" s="8"/>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:7">
       <c r="A10" s="7" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="B10" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C10" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D10" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E10">
         <v>4</v>
       </c>
       <c r="F10" s="5"/>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:7">
       <c r="A11" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" t="s">
         <v>27</v>
       </c>
-      <c r="B11" t="s">
-        <v>28</v>
-      </c>
-      <c r="C11" t="s">
-        <v>32</v>
-      </c>
       <c r="D11" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="E11">
         <v>4</v>
       </c>
       <c r="F11" s="5"/>
     </row>
-    <row r="12" spans="1:6" ht="15" thickBot="1">
+    <row r="12" spans="1:7" ht="15" thickBot="1">
       <c r="A12" s="6" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C12" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D12" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E12">
         <v>4</v>
@@ -850,18 +878,18 @@
         <v>978186632</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="15" thickBot="1">
+    <row r="13" spans="1:7" ht="15" thickBot="1">
       <c r="A13" s="6" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C13" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D13" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E13">
         <v>4</v>
@@ -870,17 +898,17 @@
         <v>978186632</v>
       </c>
     </row>
-    <row r="14" spans="1:6">
+    <row r="14" spans="1:7">
       <c r="A14" s="10"/>
       <c r="B14" s="2"/>
       <c r="F14" s="11"/>
     </row>
-    <row r="15" spans="1:6">
+    <row r="15" spans="1:7">
       <c r="A15" s="10"/>
       <c r="B15" s="2"/>
       <c r="F15" s="11"/>
     </row>
-    <row r="16" spans="1:6">
+    <row r="16" spans="1:7">
       <c r="A16" s="10"/>
       <c r="B16" s="2"/>
       <c r="F16" s="11"/>
@@ -1182,7 +1210,9 @@
     <hyperlink ref="B2" r:id="rId2"/>
     <hyperlink ref="B12" r:id="rId3"/>
     <hyperlink ref="B13" r:id="rId4"/>
+    <hyperlink ref="B3" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId6"/>
 </worksheet>
 </file>